--- a/output/laminas_comunales/comunal_o_ocup_a_2024_magallanes.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2024_magallanes.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,67 +384,67 @@
         </is>
       </c>
       <c r="C2">
-        <v>62.568306010929</v>
+        <v>75.78125</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12303</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Timaukel</t>
+          <t>Río Verde</t>
         </is>
       </c>
       <c r="C3">
-        <v>53.7234042553192</v>
+        <v>71.7948717948718</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12402</t>
+          <t>12303</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Torres del Paine</t>
+          <t>Timaukel</t>
         </is>
       </c>
       <c r="C4">
-        <v>50.787037037037</v>
+        <v>70.6666666666667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12301</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Porvenir</t>
+          <t>Río Verde</t>
         </is>
       </c>
       <c r="C5">
-        <v>45.2709319405908</v>
+        <v>68.8888888888889</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12302</t>
+          <t>12303</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Primavera</t>
+          <t>Timaukel</t>
         </is>
       </c>
       <c r="C6">
-        <v>43.4466019417476</v>
+        <v>66.16161616161619</v>
       </c>
     </row>
     <row r="7">
@@ -459,67 +459,967 @@
         </is>
       </c>
       <c r="C7">
-        <v>41.348195329087</v>
+        <v>64.5833333333333</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12104</t>
+          <t>12302</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>San Gregorio</t>
+          <t>Primavera</t>
         </is>
       </c>
       <c r="C8">
-        <v>40.2284263959391</v>
+        <v>64.2361111111111</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>12301</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Punta Arenas</t>
+          <t>Porvenir</t>
         </is>
       </c>
       <c r="C9">
-        <v>39.858084587342</v>
+        <v>63.6454529647018</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Natales</t>
+          <t>Río Verde</t>
         </is>
       </c>
       <c r="C10">
-        <v>38.5657109689263</v>
+        <v>63.2075471698113</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>12402</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Torres del Paine</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>62.7777777777778</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>62.568306010929</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12402</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Torres del Paine</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>61.1666666666667</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>57.6205523331313</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>57.1672771672772</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>12104</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>San Gregorio</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>56.4655172413793</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>55.9143985762035</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>12104</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>San Gregorio</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>55.8333333333333</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>12303</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Timaukel</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>55.6910569105691</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>55.5503980389301</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>12303</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Timaukel</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>53.7234042553192</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>53.5580524344569</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>53.2282282282282</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>52.0833333333333</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>12402</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Torres del Paine</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>51.4184397163121</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>12303</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Timaukel</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>50.9887005649718</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>50.976290097629</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>12402</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Torres del Paine</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>50.787037037037</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>12402</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Torres del Paine</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>50.0968992248062</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>12201</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Cabo de Hornos</t>
         </is>
       </c>
-      <c r="C11">
+      <c r="C30">
+        <v>46.8822843822844</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>46.3662790697674</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>46.2990151098061</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>45.2709319405908</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>44.7916666666667</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>44.0188877229801</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>12104</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>San Gregorio</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>43.8524590163934</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>43.4466019417476</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>43.3289149418474</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>41.348195329087</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>41.2236987818383</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>40.3229017359452</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>12104</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>San Gregorio</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>40.2284263959391</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>39.858084587342</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>38.5657109689263</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>38.5416666666667</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>38.2857142857143</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>37.7680652680653</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>37.3951216588757</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>36.7474181498572</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>36.3956920010732</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C51">
         <v>35.1047237076649</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>12104</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>San Gregorio</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>34.3333333333333</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>12303</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Timaukel</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>33.3333333333333</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>33.0443159922929</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>32.3316197559671</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>32.3073701842546</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>12303</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Timaukel</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>31.8452380952381</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>31.2962962962963</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>12402</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Torres del Paine</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>30.3030303030303</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>29.3478260869565</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>12104</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>San Gregorio</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>27.0833333333333</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>26.1594202898551</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>25.3676470588235</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>24.4987468671679</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>23.5849056603774</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>12104</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>San Gregorio</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>22.2727272727273</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>22.140522875817</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>12402</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Torres del Paine</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>17.0454545454545</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>16.7444364680546</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>13.7979218541516</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>10.6091370558376</v>
       </c>
     </row>
   </sheetData>
